--- a/pensum/ok09/OK09_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok09/OK09_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="161">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 9: Budsjettering og budsjettkontroll (V5)</t>
   </si>
@@ -140,18 +140,51 @@
     <t xml:space="preserve">a)  Avviket i salgsinntekt, i kroner. Inntekt: regnskap minus budsjett. Positivt tall betyr bra for resultatet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avvik inntekt = regnskap − budsjett. Avvik i % = avvik / budsjett × 100 (Økonomistyring 9.8).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Avviket i varekostnad, i kroner. Kostnad: budsjett minus regnskap. Ble kostnaden større enn planlagt, skal svaret være negativt.</t>
   </si>
   <si>
+    <t xml:space="preserve">Avvik kostnad = budsjett − regnskap (Økonomistyring 9.8: negativt avvik når kostnadene blir høyere enn budsjettert).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Avviket i driftsresultat, i kroner. Driftsresultatet behandles som en inntekt: regnskap minus budsjett.</t>
   </si>
   <si>
+    <t xml:space="preserve">Driftsresultat = driftsinntekter − driftskostnader. Avvik i driftsresultat = summen av avvikene i alle postene over (Økonomistyring 9.5, tabell 9.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Varekostnaden i prosent av salget i regnskapet: varekostnad delt på salgsinntekt. Budsjettet forutsatte 37,5 %. Svar med én desimal. Er andelen lik, fulgte kostnaden bare salget (mengdeavvik); er den høyere, har noe annet skjedd (pris, svinn, feil kalkyle).</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel av salget = post / salgsinntekt × 100. Mengdeavvik = endring i salg × budsjettert andel. Pris/forbruk = samlet avvik − mengdeavvik (Økonomistyring 9.9 om mengde- og priskomponent).</t>
+  </si>
+  <si>
     <t xml:space="preserve">e)  Hva skal Kari spørre Ida om på mandag? Skriv to setninger: ett spørsmål om materiellet og ett om andre driftskostnader.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel; bruk avvik i kroner og prosent og andel av salget (Økonomistyring 9.8–9.9).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortegnet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inntekt: regnskap − budsjett. Kostnad: budsjett − regnskap. Driftsresultatet behandles som inntekt. Ble kostnaden større enn planlagt, er avviket negativt selv om tallet «gikk opp».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andel av salget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varekostnad delt på salg, i regnskapet. Salget økte 250 000; med 37,5 % «skal» varekostnaden øke 93 750. Resten av avviket er pris eller svinn. Det er det Kari spør om.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 9, avsnitt 9.8. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -227,12 +260,21 @@
     <t xml:space="preserve">a)  Sum salgsinntekter for året, i kroner: fakturerbare timer ganger timepris, pluss materiell med påslag. De ufakturerbare timene gir ingen inntekt.</t>
   </si>
   <si>
+    <t xml:space="preserve">Salgsinntekt = forventet mengde × forventet pris (Økonomistyring 9.3.1). Salgspris materiell = innkjøp × (1 + påslag).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Lønnskostnad for året, i kroner: all lønn (også eierens) ganger 1 pluss sosiale kostnader.</t>
   </si>
   <si>
+    <t xml:space="preserve">Lønnskostnad = lønn × (1 + sats for sosiale kostnader). Satsen 46,8 % er summen av arbeidsgiveravgift, feriepenger, pensjon, helligdager, yrkesskade og sykepenger (Økonomistyring 9.3.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Driftsresultat for året, i kroner: sum salgsinntekter minus varekostnad, lønnskostnad, avskrivninger og andre driftskostnader. Renter kommer etter driftsresultatet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Driftsresultat = driftsinntekter − driftskostnader. Driftsmargin = driftsresultat × 100 / salgsinntekter (Økonomistyring kap. 4 og Formelsamling). Avskrivning = anskaffelseskost / brukstid (9.3.5).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Hvilke av disse postene hører hjemme i resultatbudsjettet (driftsbudsjettet)? Spør for hver post: er dette en inntekt eller en kostnad i driftsåret, eller er det bare penger som flytter seg?</t>
   </si>
   <si>
@@ -257,6 +299,21 @@
     <t xml:space="preserve">e)  Hvilken forutsetning er mest usikker, og hva gjør dere hvis den slår feil? To setninger. Tips: regn hva som skjer med driftsresultatet hvis hver montør fakturerer 200 timer mindre.</t>
   </si>
   <si>
+    <t xml:space="preserve">Følsomhet: endring i driftsresultat = endring i mengde × pris. Kritisk prisfall = driftsresultat / timeinntekt (sammenheng med nullpunktsanalysen i kap. 8).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lønnskostnaden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All lønn, også eierens: 2 × 560 000 + 700 000 = 1 820 000. Gang med 1,468. De 800 ufakturerbare timene er allerede betalt gjennom lønna; de gir bare mindre inntekt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hva hører hjemme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør for hver post: er det en inntekt eller en kostnad i driftsåret? Aksjekapital, lån og mva er penger som flytter seg. Renter er kostnad; avdrag er ikke.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 9, avsnitt 9.2–9.3 og kap. 2 om lønnskostnad. Oppsettet følger resultatregnskapet (NS 4102).</t>
   </si>
   <si>
@@ -326,18 +383,42 @@
     <t xml:space="preserve">a)  Innbetalt fra årets salg i februar, i kroner: to tredeler av januarsalget pluss en tredel av februarsalget, begge med mva.</t>
   </si>
   <si>
+    <t xml:space="preserve">Innbetaling = salg × 1,25 fordelt etter kredittiden (Økonomistyring 9.4.1, tabellen over kredittider).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Sum innbetalinger i mars, i kroner: innbetalt fra årets salg (februar og mars) pluss renteinntekter. Ingen gamle fordringer igjen.</t>
   </si>
   <si>
+    <t xml:space="preserve">Sum innbetalinger = innbetalinger fra salg + andre innbetalinger (Økonomistyring 9.4.1–9.4.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Beholdning på konto ved utgangen av mars, i kroner. Regn måned for måned: beholdning ved start pluss innbetalinger minus utbetalinger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Endring i beholdning = sum innbetalinger − sum utbetalinger. Beholdning ved slutt = beholdning ved start + endring (Økonomistyring 9.6.5).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Kundene brukte 54 dager året før, ikke 20. Hva skjer med resultatbudsjettet hvis det fortsetter i budsjettåret? Tenk på når inntekten føres.   A: Det blir lavere, fordi inntektene kommer senere   B: Det endres ikke med en krone   C: Det blir høyere, fordi kundene betaler renter   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Kari skal i banken på fredag. Sett de fire tiltakene i rekkefølge og begrunn det første: A kortere kredittid (bunn 1 160 400, ingen måneder i minus), B utsette utstyret (bedrer bunnen 156 885), C større kassekreditt (endrer ikke budsjettet), D 15 dager lengre leverandørkreditt (løfter bunnen 491 300).</t>
   </si>
   <si>
+    <t xml:space="preserve">Tiltak for å styrke likviditeten (Økonomistyring 9.7): fakturer tidlig, e-faktura, kortere kredittid, purr tidlig, kontantrabatt, lengre leverandørkreditt, refinansiering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innbetalingene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salg × 1,25 først. Ved 20 dager: 1/3 i salgsmåneden, 2/3 måneden etter. Februar får 2/3 av januar og 1/3 av februar. Mars har ingen gamle fordringer igjen, men 14 000 i renteinntekter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kredittid og resultat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inntekten føres når fakturaen skrives (slide 27). Kredittiden flytter bare pengene. Resultatbudsjettet endres ikke med en krone, likviditetsbudsjettet fullstendig.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 9, avsnitt 9.4–9.7. Tallene er regnearkets ark «Likviditet». Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -389,16 +470,40 @@
     <t xml:space="preserve">a)  Saldo på konto ved utgangen av januar, i kroner. Husk: med 30 dagers kredittid kommer ingen kundepenger i januar; aksjekapital og lån gjør.</t>
   </si>
   <si>
+    <t xml:space="preserve">Saldo ved slutt = saldo ved start + innbetalinger − utbetalinger (Økonomistyring 9.6.5). Låneopptak og innskudd fra eierne er innbetalinger (9.4.11 og 9.4.13).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Saldo på konto ved utgangen av mars, i kroner. Januarsalget betales i februar og februarsalget i mars, begge med mva.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ved 30 dagers kreditt: hele salget inkl. mva innbetales måneden etter (Økonomistyring 9.4.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Kundene betaler etter 60 dager i stedet for 30. Hva blir saldoen ved utgangen av februar? (Nå kommer januarsalget først i mars.)</t>
   </si>
   <si>
+    <t xml:space="preserve">Ved 60 dagers kreditt: hele salget innbetales to måneder senere (Økonomistyring 9.4.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Hvorfor står aksjekapitalen og banklånet her, men ikke i driftsbudsjettet i oppgave A2?   A: Fordi de er inntekter i oppstartsåret   B: Fordi likviditetsbudsjettet følger pengene, og driftsbudsjettet følger inntekter og kostnader   C: Fordi de er fradragsberettiget   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Hva forfaller 10. april, og hvor mye? Regn: utgående mva på salget i januar og februar, minus inngående mva på utstyr og materiell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mva til betaling = utgående mva − inngående mva. Mva i et beløp inkl. mva = beløpet × 0,2 (Økonomistyring 9.2.2 og 9.4.7, tabell 9.7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hva kommer inn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Januar: bare aksjekapital og lån. Februar: januarsalget × 1,25 = 437 500. Mars: februarsalget × 1,25 = 500 000. Marssalget kommer i april.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mva-terminen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utgående mva = salg × 25 %. Inngående = mva på utstyr og materiell (beløpet inkl. mva × 0,2). Netto betales 10. april. Mva står aldri i resultatbudsjettet.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 9, avsnitt 9.4–9.6. Terminer: arbeidsgiveravgift 15. mars for januar–februar, mva 10. april for januar–februar (Skatteetaten).</t>
@@ -412,7 +517,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,8 +584,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -496,13 +623,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -555,7 +700,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -624,7 +769,27 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -681,8 +846,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -696,7 +861,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -710,7 +875,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1013,7 +1178,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1171,35 +1336,20 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(-189000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="B18" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(-50368))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+    </row>
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
         <v>40</v>
       </c>
@@ -1209,82 +1359,207 @@
       <c r="E20" s="7"/>
       <c r="F20" s="15"/>
       <c r="G20" s="16" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(39))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F20="","",IF(ABS(F20-(-189000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-    </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="16" t="str">
+        <f aca="false">IF(F23="","",IF(ABS(F23-(-50368))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="16" t="str">
+        <f aca="false">IF(F26="","",IF(ABS(F26-(39))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+    </row>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+    </row>
+    <row r="40" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="20">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:G24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1301,7 +1576,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1312,7 +1587,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1322,7 +1597,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1333,7 +1608,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1344,10 +1619,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -1356,11 +1631,11 @@
       <c r="G7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>49</v>
+      <c r="A8" s="23" t="s">
+        <v>60</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1369,11 +1644,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>51</v>
+      <c r="A9" s="23" t="s">
+        <v>62</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1382,11 +1657,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>53</v>
+      <c r="A10" s="23" t="s">
+        <v>64</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1395,11 +1670,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>55</v>
+      <c r="A11" s="23" t="s">
+        <v>66</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1408,11 +1683,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>57</v>
+      <c r="A12" s="23" t="s">
+        <v>68</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1421,11 +1696,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>59</v>
+      <c r="A13" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1434,11 +1709,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="23" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1447,11 +1722,11 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>62</v>
+      <c r="A15" s="23" t="s">
+        <v>73</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1460,11 +1735,11 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>64</v>
+      <c r="A16" s="23" t="s">
+        <v>75</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -1489,7 +1764,7 @@
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1501,187 +1776,276 @@
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(2671760))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16" t="str">
-        <f aca="false">IF(F21="","",IF(ABS(F21-(144240))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+    </row>
+    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="16" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
+      <c r="F22" s="15"/>
+      <c r="G22" s="16" t="str">
+        <f aca="false">IF(F22="","",IF(ABS(F22-(2671760))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="16" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="19"/>
+      <c r="F25" s="15"/>
       <c r="G25" s="16" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F25="","",IF(ABS(F25-(144240))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="16" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="16" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+    </row>
+    <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="16" t="str">
-        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-    </row>
-    <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="16" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="16" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="16" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="16" t="str">
+        <f aca="false">IF(F32="","",IF(UPPER(TRIM(F32))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="16" t="str">
+        <f aca="false">IF(F33="","",IF(UPPER(TRIM(F33))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="16" t="str">
+        <f aca="false">IF(F34="","",IF(UPPER(TRIM(F34))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="19"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+    </row>
+    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+    </row>
+    <row r="46" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="34">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1696,19 +2060,26 @@
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B23:G23"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="B26:G26"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A30:G32"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A47:G47"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1725,7 +2096,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1736,7 +2107,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1746,7 +2117,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1757,7 +2128,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1768,21 +2139,21 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -1790,7 +2161,7 @@
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>2520000</v>
@@ -1804,7 +2175,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>0</v>
@@ -1817,8 +2188,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>88</v>
+      <c r="A11" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -1826,7 +2197,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>2100000</v>
@@ -1840,7 +2211,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B13" s="13" t="n">
         <v>700000</v>
@@ -1854,7 +2225,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>136000</v>
@@ -1868,7 +2239,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13" t="n">
         <v>0</v>
@@ -1882,7 +2253,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>156250</v>
@@ -1896,7 +2267,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="B17" s="13" t="n">
         <v>0</v>
@@ -1910,7 +2281,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="B18" s="11" t="n">
         <v>0</v>
@@ -1924,7 +2295,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="B19" s="13" t="n">
         <v>0</v>
@@ -1937,22 +2308,22 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="22" t="n">
+      <c r="A20" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="27" t="n">
         <v>3092250</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="27" t="n">
         <v>2892425</v>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="27" t="n">
         <v>2830525</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="B21" s="13" t="n">
         <v>982650</v>
@@ -1961,8 +2332,8 @@
       <c r="D21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
-        <v>98</v>
+      <c r="A22" s="26" t="s">
+        <v>117</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -1996,7 +2367,7 @@
     </row>
     <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2008,120 +2379,216 @@
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16" t="str">
-        <f aca="false">IF(F27="","",IF(ABS(F27-(2680667))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="16" t="str">
-        <f aca="false">IF(F28="","",IF(ABS(F28-(2173117))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+    </row>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
-      <c r="F29" s="19"/>
+      <c r="F29" s="15"/>
       <c r="G29" s="16" t="str">
-        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F29="","",IF(ABS(F29-(2680667))&lt;=1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-    </row>
-    <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
+    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+    </row>
+    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="16" t="str">
+        <f aca="false">IF(F32="","",IF(ABS(F32-(2173117))&lt;=1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="16" t="str">
+        <f aca="false">IF(F35="","",IF(UPPER(TRIM(F35))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="19"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="19"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+    </row>
+    <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+    </row>
+    <row r="47" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="B27:G27"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A31:G33"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A48:G48"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2138,7 +2605,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2149,7 +2616,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2159,7 +2626,7 @@
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2170,7 +2637,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2181,21 +2648,21 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>300000</v>
@@ -2209,7 +2676,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>500000</v>
@@ -2223,15 +2690,15 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>88</v>
+      <c r="A11" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -2239,7 +2706,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>375000</v>
@@ -2253,7 +2720,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="B13" s="13" t="n">
         <v>175000</v>
@@ -2267,7 +2734,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>150000</v>
@@ -2281,7 +2748,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="B15" s="13" t="n">
         <v>10000</v>
@@ -2295,7 +2762,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>12000</v>
@@ -2309,7 +2776,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="B17" s="13" t="n">
         <v>45000</v>
@@ -2323,7 +2790,7 @@
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="B18" s="11" t="n">
         <v>0</v>
@@ -2336,22 +2803,22 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="23" t="n">
+      <c r="A19" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="28" t="n">
         <v>767000</v>
       </c>
-      <c r="C19" s="23" t="n">
+      <c r="C19" s="28" t="n">
         <v>322000</v>
       </c>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="28" t="n">
         <v>364300</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="B20" s="11" t="n">
         <v>0</v>
@@ -2360,8 +2827,8 @@
       <c r="D20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
-        <v>119</v>
+      <c r="A21" s="25" t="s">
+        <v>146</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -2395,7 +2862,7 @@
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2407,120 +2874,216 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="16" t="str">
-        <f aca="false">IF(F26="","",IF(ABS(F26-(284200))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16" t="str">
-        <f aca="false">IF(F27="","",IF(ABS(F27-(-289000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="19"/>
+      <c r="F28" s="15"/>
       <c r="G28" s="16" t="str">
-        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F28="","",IF(ABS(F28-(284200))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-    </row>
-    <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+    </row>
+    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="16" t="str">
+        <f aca="false">IF(F31="","",IF(ABS(F31-(-289000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="34" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="16" t="str">
+        <f aca="false">IF(F34="","",IF(UPPER(TRIM(F34))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="19"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+    </row>
+    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+    </row>
+    <row r="46" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="B26:G26"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A30:G32"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A47:G47"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ok09/OK09_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok09/OK09_Klasseoppgaver_v5.xlsx
@@ -194,7 +194,7 @@
     <t xml:space="preserve">A2 · Din egen el-bedrift: resultatbudsjettet for første driftsår</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Resultatbudsjettet settes opp som resultatregnskapet, bare framover i tid: salgsinntekter, varekostnad, lønnskostnad, avskrivninger, andre driftskostnader, driftsresultat, finansposter. Hver linje skal ha en forutsetning bak seg. Lønnskostnaden er lønn pluss sosiale kostnader. Egenkapital, lån, mva og ufakturerbare timer hører ikke hjemme i driftsbudsjettet.</t>
+    <t xml:space="preserve">Kort oppsummert: Resultatbudsjettet settes opp som resultatregnskapet, bare framover i tid: salgsinntekter, varekostnad, lønnskostnad, avskrivninger, andre driftskostnader, driftsresultat, finansposter. Hver linje skal ha en forutsetning bak seg. Lønnskostnaden er lønn pluss sosiale kostnader. Egenkapital, lån, merverdiavgift og ufakturerbare timer hører ikke hjemme i driftsbudsjettet.</t>
   </si>
   <si>
     <t xml:space="preserve">Dere starter Fjell Elektro AS, en installasjonsbedrift med to montører og én eier som er faglig ansvarlig og selv jobber halve tiden ute på oppdrag. Forutsetningene for første driftsår står under. Sett opp resultatbudsjettet (driftsbudsjettet) som et resultatregnskap, linje for linje: salgsinntekter, varekostnad, lønnskostnad, avskrivninger, andre driftskostnader, driftsresultat, renter, resultat før skatt. Skriv én setning som begrunner hver linje. Bruk bare det som er inntekt eller kostnad i driftsåret; penger som lånes eller skytes inn, er ikke inntekt.</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">Timepris</t>
   </si>
   <si>
-    <t xml:space="preserve">890 kr per time uten mva</t>
+    <t xml:space="preserve">890 kr per time uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Materiell</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">Hva hører hjemme</t>
   </si>
   <si>
-    <t xml:space="preserve">Spør for hver post: er det en inntekt eller en kostnad i driftsåret? Aksjekapital, lån og mva er penger som flytter seg. Renter er kostnad; avdrag er ikke.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 9, avsnitt 9.2–9.3 og kap. 2 om lønnskostnad. Oppsettet følger resultatregnskapet (NS 4102).</t>
+    <t xml:space="preserve">Spør for hver post: er det en inntekt eller en kostnad i driftsåret? Aksjekapital, lån og merverdiavgift er penger som flytter seg. Renter er kostnad; avdrag er ikke.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 9, avsnitt 9.2–9.3 og kap. 2 om lønnskostnad. Oppsettet følger resultatregnskapet (Norsk Standard (NS) 4102 for kontoplan).</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys, første kvartal i budsjettåret: har vi penger til lønn den 15.?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Likviditetsbudsjettet fører pengene når de flytter seg, med mva. Sum innbetalinger − sum utbetalinger = endring i beholdning. Beholdning ved månedsstart + endring = beholdning ved månedsslutt. Ved 20 dagers kredittid kommer 1/3 av salget inkl. mva inn i salgsmåneden og 2/3 måneden etter. Feriepenger, arbeidsgiveravgift, mva og avdrag går ut av kontoen på faste datoer uten å være kostnad i perioden.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casen er lagt til budsjettåret 2027. Nordlys går inn i året med 982 650 kr på konto og 4 200 000 kr utestående hos kundene (2 520 000 kommer i januar og 1 680 000 i februar). Budsjettert salg uten mva er 1 800 000 i januar, 2 100 000 i februar og 2 200 000 i mars, med 20 dagers kredittid. Utbetalingene står ferdig i tabellen. Fyll inn innbetalingene fra kundene og regn ut beholdningen måned for måned. Gå fram slik: salg ganger 1,25 (mva), fordel etter kredittiden, legg til gamle fordringer og renteinntekter, trekk fra utbetalingene, legg endringen til beholdningen ved månedsstart.</t>
+    <t xml:space="preserve">Kort oppsummert: Likviditetsbudsjettet fører pengene når de flytter seg, med merverdiavgift. Sum innbetalinger − sum utbetalinger = endring i beholdning. Beholdning ved månedsstart + endring = beholdning ved månedsslutt. Ved 20 dagers kredittid kommer 1/3 av salget med merverdiavgift inn i salgsmåneden og 2/3 måneden etter. Feriepenger, arbeidsgiveravgift, merverdiavgift og avdrag går ut av kontoen på faste datoer uten å være kostnad i perioden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casen er lagt til budsjettåret 2027. Nordlys går inn i året med 982 650 kr på konto og 4 200 000 kr utestående hos kundene (2 520 000 kommer i januar og 1 680 000 i februar). Budsjettert salg uten merverdiavgift er 1 800 000 i januar, 2 100 000 i februar og 2 200 000 i mars, med 20 dagers kredittid. Utbetalingene står ferdig i tabellen. Fyll inn innbetalingene fra kundene og regn ut beholdningen måned for måned. Gå fram slik: salg ganger 1,25 (merverdiavgift), fordel etter kredittiden, legg til gamle fordringer og renteinntekter, trekk fra utbetalingene, legg endringen til beholdningen ved månedsstart.</t>
   </si>
   <si>
     <t xml:space="preserve">Kr</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">Mars</t>
   </si>
   <si>
-    <t xml:space="preserve">Innbetalt fra årets salg (inkl. mva)</t>
+    <t xml:space="preserve">Innbetalt fra årets salg (med merverdiavgift)</t>
   </si>
   <si>
     <t xml:space="preserve">Innbetalt fra kundefordringer 1. januar</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">= Sum innbetalinger</t>
   </si>
   <si>
-    <t xml:space="preserve">Til leverandøren (inkl. mva)</t>
+    <t xml:space="preserve">Til leverandøren (med merverdiavgift)</t>
   </si>
   <si>
     <t xml:space="preserve">Arbeidsgiveravgift (termin)</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">Merverdiavgift (termin)</t>
   </si>
   <si>
-    <t xml:space="preserve">Andre driftskostnader (inkl. mva)</t>
+    <t xml:space="preserve">Andre driftskostnader (med merverdiavgift)</t>
   </si>
   <si>
     <t xml:space="preserve">Renter og avdrag (kvartal)</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">Forhåndsskatt</t>
   </si>
   <si>
-    <t xml:space="preserve">Investering, utstyr (inkl. mva)</t>
+    <t xml:space="preserve">Investering, utstyr (med merverdiavgift)</t>
   </si>
   <si>
     <t xml:space="preserve">= Sum utbetalinger</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">= Beholdning ved månedsslutt</t>
   </si>
   <si>
-    <t xml:space="preserve">a)  Innbetalt fra årets salg i februar, i kroner: to tredeler av januarsalget pluss en tredel av februarsalget, begge med mva.</t>
+    <t xml:space="preserve">a)  Innbetalt fra årets salg i februar, i kroner: to tredeler av januarsalget pluss en tredel av februarsalget, begge med merverdiavgift.</t>
   </si>
   <si>
     <t xml:space="preserve">Innbetaling = salg × 1,25 fordelt etter kredittiden (Økonomistyring 9.4.1, tabellen over kredittider).</t>
@@ -425,10 +425,10 @@
     <t xml:space="preserve">B2 · Din egen el-bedrift: likviditeten i oppstartsmånedene</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: I oppstarten kommer pengene inn senere enn de går ut. Aksjekapital og lån er innbetalinger i likviditetsbudsjettet, selv om de aldri står i driftsbudsjettet. Alle beløp er med mva. Arbeidsgiveravgift og mva betales terminvis, ikke i måneden de oppstår.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fjell Elektro AS (samme bedrift som i oppgave A2) starter 1. januar med tom konto. Kundene får 30 dagers kredittid, så januarsalget betales i februar. Salg uten mva: januar 350 000, februar 400 000, mars 400 000. Utbetalingene per måned står i tabellen. Lønna er forenklet til 150 000 kr per måned; A2 gir 1 820 000 / 12 = 151 667, men rundingen gjør regningen enklere (arbeidsgiveravgift 14,1 % av 300 000 = 42 300). Fyll inn innbetalingene og regn ut saldoen måned for måned.</t>
+    <t xml:space="preserve">Kort oppsummert: I oppstarten kommer pengene inn senere enn de går ut. Aksjekapital og lån er innbetalinger i likviditetsbudsjettet, selv om de aldri står i driftsbudsjettet. Alle beløp er med merverdiavgift. Arbeidsgiveravgift og merverdiavgift betales terminvis, ikke i måneden de oppstår.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fjell Elektro AS (samme bedrift som i oppgave A2) starter 1. januar med tom konto. Kundene får 30 dagers kredittid, så januarsalget betales i februar. Salg uten merverdiavgift: januar 350 000, februar 400 000, mars 400 000. Utbetalingene per måned står i tabellen. Lønna er forenklet til 150 000 kr per måned; A2 gir 1 820 000 / 12 = 151 667, men rundingen gjør regningen enklere (arbeidsgiveravgift 14,1 % av 300 000 = 42 300). Fyll inn innbetalingene og regn ut saldoen måned for måned.</t>
   </si>
   <si>
     <t xml:space="preserve">Innbetalt aksjekapital</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">Utbetalt banklån</t>
   </si>
   <si>
-    <t xml:space="preserve">Innbetalt fra kunder (inkl. mva)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utstyr og verktøy (300 000 + mva)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiell (inkl. mva)</t>
+    <t xml:space="preserve">Innbetalt fra kunder (med merverdiavgift)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utstyr og verktøy (300 000 + merverdiavgift)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiell (med merverdiavgift)</t>
   </si>
   <si>
     <t xml:space="preserve">Lønn utbetalt (forenklet: 150 000)</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">Saldo ved slutt = saldo ved start + innbetalinger − utbetalinger (Økonomistyring 9.6.5). Låneopptak og innskudd fra eierne er innbetalinger (9.4.11 og 9.4.13).</t>
   </si>
   <si>
-    <t xml:space="preserve">b)  Saldo på konto ved utgangen av mars, i kroner. Januarsalget betales i februar og februarsalget i mars, begge med mva.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ved 30 dagers kreditt: hele salget inkl. mva innbetales måneden etter (Økonomistyring 9.4.1).</t>
+    <t xml:space="preserve">b)  Saldo på konto ved utgangen av mars, i kroner. Januarsalget betales i februar og februarsalget i mars, begge med merverdiavgift.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ved 30 dagers kreditt: hele salget med merverdiavgift innbetales måneden etter (Økonomistyring 9.4.1).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Kundene betaler etter 60 dager i stedet for 30. Hva blir saldoen ved utgangen av februar? (Nå kommer januarsalget først i mars.)</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">d)  Hvorfor står aksjekapitalen og banklånet her, men ikke i driftsbudsjettet i oppgave A2?   A: Fordi de er inntekter i oppstartsåret   B: Fordi likviditetsbudsjettet følger pengene, og driftsbudsjettet følger inntekter og kostnader   C: Fordi de er fradragsberettiget   (skriv bokstaven)</t>
   </si>
   <si>
-    <t xml:space="preserve">e)  Hva forfaller 10. april, og hvor mye? Regn: utgående mva på salget i januar og februar, minus inngående mva på utstyr og materiell.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mva til betaling = utgående mva − inngående mva. Mva i et beløp inkl. mva = beløpet × 0,2 (Økonomistyring 9.2.2 og 9.4.7, tabell 9.7).</t>
+    <t xml:space="preserve">e)  Hva forfaller 10. april, og hvor mye? Regn: utgående merverdiavgift på salget i januar og februar, minus inngående merverdiavgift på utstyr og materiell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merverdiavgift til betaling = utgående merverdiavgift − inngående merverdiavgift. Merverdiavgift i et beløp med merverdiavgift = beløpet × 0,2 (Økonomistyring 9.2.2 og 9.4.7, tabell 9.7).</t>
   </si>
   <si>
     <t xml:space="preserve">Hva kommer inn</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">Januar: bare aksjekapital og lån. Februar: januarsalget × 1,25 = 437 500. Mars: februarsalget × 1,25 = 500 000. Marssalget kommer i april.</t>
   </si>
   <si>
-    <t xml:space="preserve">Mva-terminen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utgående mva = salg × 25 %. Inngående = mva på utstyr og materiell (beløpet inkl. mva × 0,2). Netto betales 10. april. Mva står aldri i resultatbudsjettet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 9, avsnitt 9.4–9.6. Terminer: arbeidsgiveravgift 15. mars for januar–februar, mva 10. april for januar–februar (Skatteetaten).</t>
+    <t xml:space="preserve">Merverdiavgiftsterminen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utgående merverdiavgift = salg × 25 %. Inngående = merverdiavgift på utstyr og materiell (beløpet med merverdiavgift × 0,2). Netto betales 10. april. Merverdiavgift står aldri i resultatbudsjettet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 9, avsnitt 9.4–9.6. Terminer: arbeidsgiveravgift 15. mars for januar–februar, merverdiavgift 10. april for januar–februar (Skatteetaten).</t>
   </si>
 </sst>
 </file>
@@ -2151,7 +2151,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
         <v>104</v>
       </c>
@@ -2195,7 +2195,7 @@
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
         <v>108</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
         <v>111</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
         <v>114</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
         <v>137</v>
       </c>
@@ -2704,7 +2704,7 @@
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
         <v>138</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
         <v>38</v>
       </c>
@@ -3028,7 +3028,7 @@
       <c r="F43" s="22"/>
       <c r="G43" s="22"/>
     </row>
-    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
         <v>158</v>
       </c>

--- a/pensum/ok09/OK09_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok09/OK09_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="161">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 9: Budsjettering og budsjettkontroll (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 9: Budsjettering og budsjettkontroll (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ok09/OK09_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok09/OK09_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Budsjettkontroll er å sette regnskapet ved siden av budsjettet for samme periode og regne avviket. Fortegnet sier om avviket er godt eller dårlig for resultatet: inntekt regnskap − budsjett, kostnad budsjett − regnskap. Avvik i prosent er avviket delt på budsjettet. Varekostnad og lønn følger salget, så se på andelen av salget før du leter etter årsaken.</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til budsjettåret 2027; regnestykket er det samme uansett når du gjør det. Første kvartal er over. Budsjettet for kvartalet er hentet fra Nordlys' resultatbudsjett, måned for måned (januar 1 800 000, februar 2 100 000 og mars 2 200 000 i salg). Regnskapet for kvartalet ligger ved siden av. Kari (daglig leder) skal møte Ida (kalkulatør og innkjøp) på mandag og vil vite hva hun skal spørre om. Gå fram slik: først avviket i kroner med riktig fortegn, så i prosent, så kostnadene som andel av salget. Først da vet du hvor du skal lete.</t>
+    <t xml:space="preserve">Casen er lagt til budsjettåret 2027; regnestykket er det samme uansett når du gjør det. Første kvartal er over. Budsjettet for kvartalet er hentet fra Nordlys' resultatbudsjett, måned for måned (januar 1 800 000, februar 2 100 000 og mars 2 200 000 i salg): varekostnaden er 37,5 % av salget, lønnskostnaden og andre driftskostnader er en fjerdedel av årsbeløpene 10 734 528 og 1 500 000, og avskrivningene er tre måneder à 620 000 / 12 pluss 10 000 for termograferingsutstyret i mars. Regnskapet for kvartalet ligger ved siden av. Kari (daglig leder) skal møte Ida (kalkulatør og innkjøp) på mandag og vil vite hva hun skal spørre om. Gå fram slik: først avviket i kroner med riktig fortegn, så i prosent, så kostnadene som andel av salget. Først da vet du hvor du skal lete.</t>
   </si>
   <si>
     <t xml:space="preserve">Post (kr)</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">Kort oppsummert: Likviditetsbudsjettet fører pengene når de flytter seg, med merverdiavgift. Sum innbetalinger − sum utbetalinger = endring i beholdning. Beholdning ved månedsstart + endring = beholdning ved månedsslutt. Ved 20 dagers kredittid kommer 1/3 av salget med merverdiavgift inn i salgsmåneden og 2/3 måneden etter. Feriepenger, arbeidsgiveravgift, merverdiavgift og avdrag går ut av kontoen på faste datoer uten å være kostnad i perioden.</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til budsjettåret 2027. Nordlys går inn i året med 982 650 kr på konto og 4 200 000 kr utestående hos kundene (2 520 000 kommer i januar og 1 680 000 i februar). Budsjettert salg uten merverdiavgift er 1 800 000 i januar, 2 100 000 i februar og 2 200 000 i mars, med 20 dagers kredittid. Utbetalingene står ferdig i tabellen. Fyll inn innbetalingene fra kundene og regn ut beholdningen måned for måned. Gå fram slik: salg ganger 1,25 (merverdiavgift), fordel etter kredittiden, legg til gamle fordringer og renteinntekter, trekk fra utbetalingene, legg endringen til beholdningen ved månedsstart.</t>
+    <t xml:space="preserve">Casen er lagt til budsjettåret 2027. Nordlys går inn i året med 982 650 kr på konto og 4 200 000 kr utestående hos kundene (2 520 000 kommer i januar og 1 680 000 i februar). Budsjettert salg uten merverdiavgift er 1 800 000 i januar, 2 100 000 i februar og 2 200 000 i mars, med 20 dagers kredittid. Utbetalingene står ferdig i tabellen: leverandøren får materiellet (37,5 % av salget, med merverdiavgift) med 30 dagers kreditt, arbeidsgiveravgift 136 000 og merverdiavgift 1 064 000 er siste termin fra i fjor, forhåndsskatten 128 425 er halvparten av fjorårets skatt på 256 850, og arbeidsgiveravgiften i mars er 2 × 14,1 % × 700 000. Fyll inn innbetalingene fra kundene og regn ut beholdningen måned for måned. Gå fram slik: salg ganger 1,25 (merverdiavgift), fordel etter kredittiden, legg til gamle fordringer og renteinntekter, trekk fra utbetalingene, legg endringen til beholdningen ved månedsstart.</t>
   </si>
   <si>
     <t xml:space="preserve">Kr</t>
@@ -1208,7 +1208,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>23</v>
       </c>
@@ -2126,7 +2126,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>99</v>
       </c>
